--- a/downloads/samples/CTC_Source_Registry_SAMPLE.xlsx
+++ b/downloads/samples/CTC_Source_Registry_SAMPLE.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Standing row in every registry. Readers submit events through the CTC form; harvest reads this chapter's rows from the shared view each week. Never delete.</t>
+          <t>Standing row in every source list. Readers submit events through the CTC form; harvest reads this chapter's rows from the shared view each week. Never delete.</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
